--- a/test/Compatibility.xlsx
+++ b/test/Compatibility.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="WinMM" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Platform</t>
   </si>
@@ -221,7 +221,19 @@
     <t xml:space="preserve">Callisto Protocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Sora No Kiseki the 1st</t>
+    <t xml:space="preserve">Trails in the Sky 1st Chapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tormented Souls 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game check if controller present only once on startup with GetState() x 4 slot, no controller hot reload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Persona 5 Royal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sora No Kiseki the 1st (Demo)</t>
   </si>
   <si>
     <t xml:space="preserve">GBE Fork/Experimental (default action set) SteamInput -&gt; XInput | Loads xinput1_4.dll | No XInput fallback without conversion ?</t>
@@ -243,6 +255,12 @@
   </si>
   <si>
     <t xml:space="preserve">RUNE (SteamInput ?) -&gt; XInput (InputFusion.dll injected/XInput hook)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jump Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Need action set (?)</t>
   </si>
   <si>
     <t xml:space="preserve">Stalkers 2</t>
@@ -447,12 +465,12 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -958,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="18"/>
     <col customWidth="1" min="3" max="3" width="45"/>
@@ -1028,7 +1046,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F5" t="s">
@@ -1046,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F6" t="s">
@@ -1064,7 +1082,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1115,8 +1133,8 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="s">
@@ -1133,8 +1151,8 @@
       <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F4" t="s">
@@ -1151,8 +1169,8 @@
       <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F5" t="s">
@@ -1170,7 +1188,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1185,7 +1203,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1236,8 +1254,8 @@
       <c r="C3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F3" t="s">
@@ -1254,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="41.42578125"/>
     <col customWidth="1" min="4" max="4" width="18.85546875"/>
@@ -1292,7 +1310,7 @@
         <v>29</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F3" t="s">
@@ -1310,7 +1328,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F4" t="s">
@@ -1328,7 +1346,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F5" t="s">
@@ -1346,7 +1364,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1361,7 +1379,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F7" t="s">
@@ -1379,7 +1397,7 @@
         <v>38</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1394,7 +1412,7 @@
         <v>39</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1409,7 +1427,7 @@
         <v>40</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1423,8 +1441,8 @@
       <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F11" t="s">
@@ -1442,7 +1460,7 @@
         <v>43</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1456,10 +1474,10 @@
       <c r="C13" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1473,10 +1491,10 @@
       <c r="C14" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1490,10 +1508,10 @@
       <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1508,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="D16" s="6"/>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1520,8 +1538,56 @@
         <v>50</v>
       </c>
       <c r="D17" s="6"/>
-      <c r="E17" s="10" t="s">
-        <v>30</v>
+      <c r="E17" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="15">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>3375780</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" ht="15">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>2464280</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1687950</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1537,7 +1603,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="10.8515625"/>
-    <col customWidth="1" min="3" max="3" width="24.57421875"/>
+    <col customWidth="1" min="3" max="3" width="29.28125"/>
     <col customWidth="1" min="4" max="4" width="16.57421875"/>
     <col customWidth="1" min="5" max="5" width="10.8515625"/>
     <col customWidth="1" min="6" max="6" width="154.421875"/>
@@ -1568,17 +1634,17 @@
         <v>9</v>
       </c>
       <c r="B3" s="7">
-        <v>3447040</v>
+        <v>3920660</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -1589,14 +1655,14 @@
         <v>740130</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" ht="14.25">
@@ -1607,14 +1673,14 @@
         <v>275850</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="14.25">
@@ -1625,14 +1691,32 @@
         <v>2523720</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1757300</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1678,7 +1762,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/test/Compatibility.xlsx
+++ b/test/Compatibility.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="WinMM" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>Platform</t>
   </si>
@@ -32,6 +32,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Game version</t>
+  </si>
+  <si>
     <t xml:space="preserve">API Compatibility</t>
   </si>
   <si>
@@ -50,6 +53,9 @@
     <t>Gex</t>
   </si>
   <si>
+    <t>OOBE</t>
+  </si>
+  <si>
     <t>Steam</t>
   </si>
   <si>
@@ -65,6 +71,9 @@
     <t xml:space="preserve">Alone In The Dark: The New Nightmare</t>
   </si>
   <si>
+    <t>Manual</t>
+  </si>
+  <si>
     <t>0.3.0dev</t>
   </si>
   <si>
@@ -74,7 +83,7 @@
     <t xml:space="preserve">Peter Jackson's King Kong - Signature Edition</t>
   </si>
   <si>
-    <t xml:space="preserve">Axes are hard-coded (camera)</t>
+    <t xml:space="preserve">Axes are hard-coded (camera) and change if vid == microsoft (xbox)</t>
   </si>
   <si>
     <t xml:space="preserve">M&amp;Ms The Lost Formulas</t>
@@ -83,6 +92,9 @@
     <t xml:space="preserve">Resident Evil</t>
   </si>
   <si>
+    <t>SOS</t>
+  </si>
+  <si>
     <t>0.3.0</t>
   </si>
   <si>
@@ -101,6 +113,9 @@
     <t xml:space="preserve">Dino Crisis</t>
   </si>
   <si>
+    <t xml:space="preserve">Fixme: KBM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dino Crisis 2</t>
   </si>
   <si>
@@ -110,10 +125,40 @@
     <t xml:space="preserve">crash on create device mouse</t>
   </si>
   <si>
+    <t>Greedfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crash on first GetDeviceState() call if pov != 0  | button layout is messed up</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resident Evil HD Remaster</t>
   </si>
   <si>
     <t>0.2.0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Might pick up Dinput before Xinput (rarely) resulting in messed up controls, fixed by running </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GAMEPAD_API_DINPUT8=HOOK</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident Evil 0 HD REMASTER</t>
   </si>
   <si>
     <r>
@@ -129,9 +174,6 @@
       </rPr>
       <t>GAMEPAD_API_DINPUT8=HOOK</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident Evil 0 HD REMASTER</t>
   </si>
   <si>
     <t xml:space="preserve">TTG The Walking Dead</t>
@@ -194,7 +236,25 @@
     <t xml:space="preserve">Fuga : Melodies of Steel 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Enumerate all Xinput slots via XInputGetCapabilities() before SDL is ready resulting in the game thinking there are no gamepads thus no need to poll for gamepad input</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">On startup check only once XInputGetState() x4 slots before SDL is ready | no controller hot reload  -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GAMEP_API_XINPUT_CONNECTED=ALWAYS</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Twilight Monk </t>
@@ -227,12 +287,81 @@
     <t xml:space="preserve">Tormented Souls 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Game check if controller present only once on startup with GetState() x 4 slot, no controller hot reload</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">no controller hot reload -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GAMEP_API_XINPUT_CONNECTED=ALWAYS</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Persona 5 Royal</t>
   </si>
   <si>
+    <t>Overcooked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">build 2270609</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Need </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GAMEPAD_API_XINPUT=HOOK</t>
+    </r>
+  </si>
+  <si>
+    <t>Gunbrella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build 12203677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hollow Knight</t>
+  </si>
+  <si>
+    <t>1.5.12620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XInput must be enabled in game's settings menu under gamepad &gt; advanced</t>
+  </si>
+  <si>
+    <t>Dispatch</t>
+  </si>
+  <si>
+    <t>1.0.16838</t>
+  </si>
+  <si>
+    <t>GAMEPAD_API_XINPUT=HOOK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sora No Kiseki the 1st (Demo)</t>
   </si>
   <si>
@@ -261,16 +390,13 @@
   </si>
   <si>
     <t xml:space="preserve">Need action set (?)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stalkers 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -295,8 +421,28 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,11 +466,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -344,6 +502,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -434,54 +607,69 @@
       <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="4" fillId="5" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="5" fillId="6" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="7" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf fontId="0" fillId="7" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="4" borderId="1" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="4" borderId="1" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="5" fillId="6" borderId="0" numFmtId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="6">
     <cellStyle name="Entrée" xfId="1" builtinId="20"/>
     <cellStyle name="Insatisfaisant" xfId="2" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Satisfaisant" xfId="3" builtinId="26"/>
+    <cellStyle name="Check Cell" xfId="4" builtinId="23"/>
+    <cellStyle name="Neutral" xfId="5" builtinId="28"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -981,8 +1169,9 @@
     <col customWidth="1" min="2" max="2" width="18"/>
     <col customWidth="1" min="3" max="3" width="45"/>
     <col customWidth="1" min="4" max="4" width="18.5703125"/>
-    <col customWidth="1" min="5" max="5" width="10.28515625"/>
-    <col customWidth="1" min="6" max="6" width="152.28515625"/>
+    <col customWidth="1" min="5" max="5" width="25.421875"/>
+    <col customWidth="1" min="6" max="6" width="15.28125"/>
+    <col customWidth="1" min="7" max="7" width="171.7109375"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -998,92 +1187,105 @@
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8">
         <v>247660</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="8"/>
+        <v>12</v>
+      </c>
       <c r="E4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
         <v>15</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="8"/>
+        <v>19</v>
+      </c>
       <c r="E6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="9" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1100,7 +1302,9 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="39.42578125"/>
     <col customWidth="1" min="4" max="4" width="18"/>
-    <col customWidth="1" min="6" max="6" width="117.7109375"/>
+    <col customWidth="1" min="5" max="5" width="19.140625"/>
+    <col customWidth="1" min="6" max="6" width="16.57421875"/>
+    <col customWidth="1" min="7" max="7" width="162.421875"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1116,95 +1320,114 @@
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="F5" s="10" t="s">
         <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="9" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="9" t="s">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1217,11 +1440,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="31.5703125"/>
     <col customWidth="1" min="4" max="4" width="18.7109375"/>
-    <col customWidth="1" min="6" max="6" width="127.7109375"/>
+    <col customWidth="1" min="5" max="5" width="17.28125"/>
+    <col customWidth="1" min="6" max="6" width="13.00390625"/>
+    <col customWidth="1" min="7" max="7" width="171.57421875"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1237,29 +1462,54 @@
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7">
+        <v>11</v>
+      </c>
+      <c r="B3" s="8">
         <v>12160</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="15">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8">
+        <v>606880</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1526,9 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="41.42578125"/>
     <col customWidth="1" min="4" max="4" width="18.85546875"/>
-    <col customWidth="1" min="6" max="6" width="207"/>
+    <col customWidth="1" min="5" max="5" width="17.421875"/>
+    <col customWidth="1" min="6" max="6" width="19.28125"/>
+    <col customWidth="1" min="7" max="7" width="199.8515625"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1289,305 +1541,436 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7">
+        <v>11</v>
+      </c>
+      <c r="B3" s="8">
         <v>304240</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8">
         <v>339340</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
+        <v>39</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7">
+        <v>11</v>
+      </c>
+      <c r="B5" s="8">
         <v>1449690</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8">
         <v>2679460</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="9" t="s">
-        <v>30</v>
+        <v>43</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8">
         <v>731490</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8">
         <v>753640</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="9" t="s">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7">
+        <v>11</v>
+      </c>
+      <c r="B9" s="8">
         <v>1623730</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="9" t="s">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7">
+        <v>11</v>
+      </c>
+      <c r="B10" s="8">
         <v>1150440</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="9" t="s">
-        <v>30</v>
+        <v>48</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8">
         <v>3081320</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8">
         <v>1911940</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="9" t="s">
-        <v>30</v>
+        <v>51</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7">
+        <v>11</v>
+      </c>
+      <c r="B13" s="8">
         <v>219990</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8">
         <v>1245620</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>30</v>
+        <v>54</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8">
         <v>1144200</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>30</v>
+        <v>55</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7">
+        <v>11</v>
+      </c>
+      <c r="B16" s="8">
         <v>1874000</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="9" t="s">
-        <v>30</v>
+        <v>56</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="15">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="9" t="s">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="15">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7">
+        <v>11</v>
+      </c>
+      <c r="B18" s="8">
         <v>3375780</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="9" t="s">
-        <v>20</v>
+        <v>59</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="15">
       <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7">
+        <v>11</v>
+      </c>
+      <c r="B19" s="8">
         <v>2464280</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="7">
+      <c r="A20" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="8">
         <v>1687950</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="9" t="s">
-        <v>20</v>
+        <v>62</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="8">
+        <v>448510</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="8">
+        <v>1580180</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="8">
+        <v>367520</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="8">
+        <v>2592160</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1605,8 +1988,9 @@
     <col customWidth="1" min="2" max="2" width="10.8515625"/>
     <col customWidth="1" min="3" max="3" width="29.28125"/>
     <col customWidth="1" min="4" max="4" width="16.57421875"/>
-    <col customWidth="1" min="5" max="5" width="10.8515625"/>
-    <col customWidth="1" min="6" max="6" width="154.421875"/>
+    <col customWidth="1" min="5" max="5" width="18.140625"/>
+    <col customWidth="1" min="6" max="6" width="13.7109375"/>
+    <col customWidth="1" min="7" max="7" width="200.8515625"/>
   </cols>
   <sheetData>
     <row r="2" ht="14.25">
@@ -1616,107 +2000,120 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7">
+        <v>11</v>
+      </c>
+      <c r="B3" s="8">
         <v>3920660</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
+      <c r="C3" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8">
         <v>740130</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
+        <v>76</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7">
+        <v>11</v>
+      </c>
+      <c r="B5" s="8">
         <v>275850</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>60</v>
+        <v>78</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8">
         <v>2523720</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
+        <v>80</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8">
         <v>1757300</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>64</v>
+        <v>82</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1733,8 +2130,9 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="23.85546875"/>
     <col customWidth="1" min="4" max="4" width="20.7109375"/>
-    <col customWidth="1" min="5" max="5" width="9"/>
-    <col customWidth="1" min="6" max="6" width="122.85546875"/>
+    <col customWidth="1" min="5" max="5" width="18.421875"/>
+    <col customWidth="1" min="6" max="6" width="14.7109375"/>
+    <col customWidth="1" min="7" max="7" width="183.140625"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1750,19 +2148,14 @@
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/test/Compatibility.xlsx
+++ b/test/Compatibility.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="WinMM" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>Platform</t>
   </si>
@@ -360,6 +360,18 @@
   </si>
   <si>
     <t>GAMEPAD_API_XINPUT=HOOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident Evil 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build 22277314</t>
+  </si>
+  <si>
+    <t>0.4.0</t>
+  </si>
+  <si>
+    <t>REANIMAL</t>
   </si>
   <si>
     <t xml:space="preserve">Sora No Kiseki the 1st (Demo)</t>
@@ -615,15 +627,12 @@
     <xf fontId="4" fillId="5" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="5" fillId="6" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="7" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -661,7 +670,6 @@
     <xf fontId="0" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Entrée" xfId="1" builtinId="20"/>
@@ -1184,16 +1192,16 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1207,7 +1215,7 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1215,16 +1223,16 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>247660</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
@@ -1241,10 +1249,10 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
@@ -1261,10 +1269,10 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
@@ -1281,10 +1289,10 @@
       <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1317,16 +1325,16 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1340,10 +1348,10 @@
       <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>24</v>
       </c>
       <c r="G3" t="s">
@@ -1360,10 +1368,10 @@
       <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
@@ -1380,10 +1388,10 @@
       <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
@@ -1400,10 +1408,10 @@
       <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="G6" t="s">
@@ -1420,13 +1428,13 @@
       <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="12" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1459,16 +1467,16 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1476,16 +1484,16 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>12160</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
@@ -1496,16 +1504,16 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>606880</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
@@ -1544,13 +1552,13 @@
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1558,16 +1566,16 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>304240</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G3" t="s">
@@ -1578,16 +1586,16 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>339340</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G4" t="s">
@@ -1598,16 +1606,16 @@
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>1449690</v>
       </c>
       <c r="C5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="10" t="s">
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G5" t="s">
@@ -1618,16 +1626,16 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>2679460</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1635,16 +1643,16 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>731490</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G7" t="s">
@@ -1655,16 +1663,16 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>753640</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10" t="s">
+      <c r="E8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1672,16 +1680,16 @@
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>1623730</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="10" t="s">
+      <c r="E9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1689,16 +1697,16 @@
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>1150440</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="E10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1706,16 +1714,16 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>3081320</v>
       </c>
       <c r="C11" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="10" t="s">
+      <c r="E11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
@@ -1726,16 +1734,16 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>1911940</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="10" t="s">
+      <c r="E12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1743,16 +1751,16 @@
       <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>219990</v>
       </c>
       <c r="C13" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="10" t="s">
+      <c r="E13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G13" t="s">
@@ -1763,16 +1771,16 @@
       <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>1245620</v>
       </c>
       <c r="C14" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="10" t="s">
+      <c r="E14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G14" t="s">
@@ -1783,16 +1791,16 @@
       <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>1144200</v>
       </c>
       <c r="C15" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="10" t="s">
+      <c r="E15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G15" t="s">
@@ -1803,16 +1811,16 @@
       <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>1874000</v>
       </c>
       <c r="C16" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="10" t="s">
+      <c r="E16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1823,10 +1831,10 @@
       <c r="C17" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="10" t="s">
+      <c r="E17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1834,16 +1842,16 @@
       <c r="A18" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>3375780</v>
       </c>
       <c r="C18" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="10" t="s">
+      <c r="E18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1851,16 +1859,16 @@
       <c r="A19" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>2464280</v>
       </c>
       <c r="C19" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="10" t="s">
+      <c r="E19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
@@ -1868,19 +1876,19 @@
       </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="A20" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="7">
         <v>1687950</v>
       </c>
       <c r="C20" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="10" t="s">
+      <c r="E20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1888,19 +1896,19 @@
       <c r="A21" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="7">
         <v>448510</v>
       </c>
       <c r="C21" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>24</v>
       </c>
       <c r="G21" t="s">
@@ -1911,7 +1919,7 @@
       <c r="A22" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="7">
         <v>1580180</v>
       </c>
       <c r="C22" t="s">
@@ -1920,10 +1928,10 @@
       <c r="D22" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="10" t="s">
+      <c r="E22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1931,7 +1939,7 @@
       <c r="A23" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <v>367520</v>
       </c>
       <c r="C23" t="s">
@@ -1940,10 +1948,10 @@
       <c r="D23" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
@@ -1954,7 +1962,7 @@
       <c r="A24" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="7">
         <v>2592160</v>
       </c>
       <c r="C24" t="s">
@@ -1963,14 +1971,54 @@
       <c r="D24" t="s">
         <v>72</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="10" t="s">
+      <c r="E24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="14" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="7">
+        <v>3764200</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="7">
+        <v>2129530</v>
+      </c>
+      <c r="C26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="7">
+        <v>358245</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2000,13 +2048,13 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2020,100 +2068,100 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>3920660</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="C3" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>740130</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>275850</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="17" t="s">
-        <v>79</v>
+      <c r="G5" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>2523720</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>1757300</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>83</v>
+      <c r="G7" s="12" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2145,16 +2193,16 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
